--- a/sheets/S08A22P211.xlsx
+++ b/sheets/S08A22P211.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7520" uniqueCount="1842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7520" uniqueCount="1843">
   <si>
     <t>Voter ID</t>
   </si>
@@ -3713,6 +3713,9 @@
   </si>
   <si>
     <t>Shri Krishna</t>
+  </si>
+  <si>
+    <t>HR/03/16/0165815</t>
   </si>
   <si>
     <t>Ashwani Kumar</t>
@@ -21165,10 +21168,10 @@
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="B587" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C587" t="s">
         <v>246</v>
@@ -21191,10 +21194,10 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B588" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C588" t="s">
         <v>1018</v>
@@ -21217,10 +21220,10 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B589" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C589" t="s">
         <v>57</v>
@@ -21243,13 +21246,13 @@
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B590" t="s">
         <v>1170</v>
       </c>
       <c r="C590" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D590" t="s">
         <v>11</v>
@@ -21269,7 +21272,7 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B591" t="s">
         <v>98</v>
@@ -21295,7 +21298,7 @@
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B592" t="s">
         <v>859</v>
@@ -21321,13 +21324,13 @@
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B593" t="s">
         <v>197</v>
       </c>
       <c r="C593" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D593" t="s">
         <v>11</v>
@@ -21347,10 +21350,10 @@
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B594" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C594" t="s">
         <v>1233</v>
@@ -21373,10 +21376,10 @@
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B595" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C595" t="s">
         <v>57</v>
@@ -21399,13 +21402,13 @@
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B596" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C596" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D596" t="s">
         <v>11</v>
@@ -21425,10 +21428,10 @@
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B597" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C597" t="s">
         <v>57</v>
@@ -21451,13 +21454,13 @@
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B598" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C598" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D598" t="s">
         <v>11</v>
@@ -21477,13 +21480,13 @@
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B599" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C599" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D599" t="s">
         <v>11</v>
@@ -21503,13 +21506,13 @@
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B600" t="s">
         <v>33</v>
       </c>
       <c r="C600" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D600" t="s">
         <v>11</v>
@@ -21529,13 +21532,13 @@
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B601" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C601" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D601" t="s">
         <v>11</v>
@@ -21555,13 +21558,13 @@
     </row>
     <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B602" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C602" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D602" t="s">
         <v>11</v>
@@ -21581,10 +21584,10 @@
     </row>
     <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B603" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C603" t="s">
         <v>201</v>
@@ -21607,7 +21610,7 @@
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B604" t="s">
         <v>456</v>
@@ -21633,13 +21636,13 @@
     </row>
     <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B605" t="s">
         <v>536</v>
       </c>
       <c r="C605" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D605" t="s">
         <v>11</v>
@@ -21659,13 +21662,13 @@
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B606" t="s">
         <v>261</v>
       </c>
       <c r="C606" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D606" t="s">
         <v>11</v>
@@ -21685,13 +21688,13 @@
     </row>
     <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B607" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C607" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D607" t="s">
         <v>11</v>
@@ -21711,13 +21714,13 @@
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B608" t="s">
         <v>339</v>
       </c>
       <c r="C608" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D608" t="s">
         <v>11</v>
@@ -21737,13 +21740,13 @@
     </row>
     <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B609" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C609" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D609" t="s">
         <v>11</v>
@@ -21763,13 +21766,13 @@
     </row>
     <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B610" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C610" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D610" t="s">
         <v>11</v>
@@ -21789,10 +21792,10 @@
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B611" t="s">
         <v>1283</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1282</v>
       </c>
       <c r="C611" t="s">
         <v>328</v>
@@ -21815,13 +21818,13 @@
     </row>
     <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B612" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C612" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D612" t="s">
         <v>11</v>
@@ -21841,7 +21844,7 @@
     </row>
     <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B613" t="s">
         <v>272</v>
@@ -21867,13 +21870,13 @@
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B614" t="s">
         <v>149</v>
       </c>
       <c r="C614" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D614" t="s">
         <v>11</v>
@@ -21893,13 +21896,13 @@
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B615" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C615" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D615" t="s">
         <v>11</v>
@@ -21919,13 +21922,13 @@
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B616" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C616" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D616" t="s">
         <v>11</v>
@@ -21945,13 +21948,13 @@
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B617" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C617" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D617" t="s">
         <v>11</v>
@@ -21971,13 +21974,13 @@
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B618" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C618" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D618" t="s">
         <v>11</v>
@@ -21997,13 +22000,13 @@
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B619" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C619" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D619" t="s">
         <v>11</v>
@@ -22023,13 +22026,13 @@
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B620" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C620" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D620" t="s">
         <v>11</v>
@@ -22049,13 +22052,13 @@
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B621" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="C621" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D621" t="s">
         <v>11</v>
@@ -22075,13 +22078,13 @@
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B622" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C622" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D622" t="s">
         <v>11</v>
@@ -22101,13 +22104,13 @@
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B623" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="C623" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D623" t="s">
         <v>11</v>
@@ -22127,10 +22130,10 @@
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B624" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C624" t="s">
         <v>518</v>
@@ -22153,13 +22156,13 @@
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B625" t="s">
         <v>501</v>
       </c>
       <c r="C625" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D625" t="s">
         <v>11</v>
@@ -22179,13 +22182,13 @@
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B626" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C626" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D626" t="s">
         <v>11</v>
@@ -22205,13 +22208,13 @@
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B627" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C627" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D627" t="s">
         <v>11</v>
@@ -22231,7 +22234,7 @@
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B628" t="s">
         <v>582</v>
@@ -22257,7 +22260,7 @@
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B629" t="s">
         <v>364</v>
@@ -22283,7 +22286,7 @@
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B630" t="s">
         <v>360</v>
@@ -22309,7 +22312,7 @@
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B631" t="s">
         <v>300</v>
@@ -22335,7 +22338,7 @@
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B632" t="s">
         <v>871</v>
@@ -22361,7 +22364,7 @@
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B633" t="s">
         <v>244</v>
@@ -22387,10 +22390,10 @@
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B634" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C634" t="s">
         <v>300</v>
@@ -22413,7 +22416,7 @@
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B635" t="s">
         <v>49</v>
@@ -22439,10 +22442,10 @@
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B636" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C636" t="s">
         <v>1018</v>
@@ -22465,13 +22468,13 @@
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B637" t="s">
         <v>79</v>
       </c>
       <c r="C637" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D637" t="s">
         <v>11</v>
@@ -22491,7 +22494,7 @@
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B638" t="s">
         <v>91</v>
@@ -22517,7 +22520,7 @@
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B639" t="s">
         <v>187</v>
@@ -22543,10 +22546,10 @@
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B640" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C640" t="s">
         <v>187</v>
@@ -22569,10 +22572,10 @@
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B641" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C641" t="s">
         <v>60</v>
@@ -22595,7 +22598,7 @@
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B642" t="s">
         <v>469</v>
@@ -22621,7 +22624,7 @@
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B643" t="s">
         <v>1133</v>
@@ -22647,13 +22650,13 @@
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B644" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C644" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D644" t="s">
         <v>11</v>
@@ -22673,13 +22676,13 @@
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B645" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="C645" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D645" t="s">
         <v>11</v>
@@ -22699,7 +22702,7 @@
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B646" t="s">
         <v>323</v>
@@ -22725,10 +22728,10 @@
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B647" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C647" t="s">
         <v>49</v>
@@ -22751,10 +22754,10 @@
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B648" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="C648" t="s">
         <v>323</v>
@@ -22777,7 +22780,7 @@
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B649" t="s">
         <v>716</v>
@@ -22803,7 +22806,7 @@
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B650" t="s">
         <v>261</v>
@@ -22829,10 +22832,10 @@
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B651" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C651" t="s">
         <v>957</v>
@@ -22855,10 +22858,10 @@
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B652" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C652" t="s">
         <v>866</v>
@@ -22881,10 +22884,10 @@
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B653" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C653" t="s">
         <v>716</v>
@@ -22907,13 +22910,13 @@
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B654" t="s">
         <v>71</v>
       </c>
       <c r="C654" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D654" t="s">
         <v>11</v>
@@ -22933,7 +22936,7 @@
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B655" t="s">
         <v>866</v>
@@ -22959,7 +22962,7 @@
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B656" t="s">
         <v>501</v>
@@ -22985,7 +22988,7 @@
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B657" t="s">
         <v>693</v>
@@ -23011,7 +23014,7 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B658" t="s">
         <v>497</v>
@@ -23037,10 +23040,10 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B659" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C659" t="s">
         <v>328</v>
@@ -23063,10 +23066,10 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B660" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C660" t="s">
         <v>328</v>
@@ -23089,10 +23092,10 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B661" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C661" t="s">
         <v>501</v>
@@ -23115,10 +23118,10 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B662" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C662" t="s">
         <v>497</v>
@@ -23141,13 +23144,13 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B663" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="C663" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D663" t="s">
         <v>11</v>
@@ -23167,10 +23170,10 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B664" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C664" t="s">
         <v>913</v>
@@ -23193,13 +23196,13 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B665" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="C665" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D665" t="s">
         <v>11</v>
@@ -23219,13 +23222,13 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B666" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C666" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D666" t="s">
         <v>11</v>
@@ -23245,13 +23248,13 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B667" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="C667" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D667" t="s">
         <v>11</v>
@@ -23271,10 +23274,10 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B668" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C668" t="s">
         <v>18</v>
@@ -23297,13 +23300,13 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B669" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="C669" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="D669" t="s">
         <v>11</v>
@@ -23323,7 +23326,7 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B670" t="s">
         <v>70</v>
@@ -23349,13 +23352,13 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B671" t="s">
         <v>280</v>
       </c>
       <c r="C671" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D671" t="s">
         <v>11</v>
@@ -23375,10 +23378,10 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B672" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C672" t="s">
         <v>953</v>
@@ -23401,7 +23404,7 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B673" t="s">
         <v>173</v>
@@ -23427,7 +23430,7 @@
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B674" t="s">
         <v>538</v>
@@ -23453,7 +23456,7 @@
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B675" t="s">
         <v>79</v>
@@ -23479,13 +23482,13 @@
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B676" t="s">
         <v>1055</v>
       </c>
       <c r="C676" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="D676" t="s">
         <v>11</v>
@@ -23505,13 +23508,13 @@
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B677" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C677" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D677" t="s">
         <v>11</v>
@@ -23531,13 +23534,13 @@
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B678" t="s">
         <v>1053</v>
       </c>
       <c r="C678" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D678" t="s">
         <v>11</v>
@@ -23557,13 +23560,13 @@
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B679" t="s">
         <v>807</v>
       </c>
       <c r="C679" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D679" t="s">
         <v>11</v>
@@ -23583,13 +23586,13 @@
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B680" t="s">
         <v>574</v>
       </c>
       <c r="C680" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D680" t="s">
         <v>11</v>
@@ -23609,10 +23612,10 @@
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B681" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C681" t="s">
         <v>1053</v>
@@ -23635,10 +23638,10 @@
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B682" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="C682" t="s">
         <v>427</v>
@@ -23661,10 +23664,10 @@
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B683" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C683" t="s">
         <v>807</v>
@@ -23687,10 +23690,10 @@
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B684" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C684" t="s">
         <v>334</v>
@@ -23713,10 +23716,10 @@
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B685" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C685" t="s">
         <v>323</v>
@@ -23739,13 +23742,13 @@
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B686" t="s">
         <v>346</v>
       </c>
       <c r="C686" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D686" t="s">
         <v>11</v>
@@ -23765,13 +23768,13 @@
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B687" t="s">
         <v>101</v>
       </c>
       <c r="C687" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D687" t="s">
         <v>11</v>
@@ -23791,13 +23794,13 @@
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B688" t="s">
         <v>122</v>
       </c>
       <c r="C688" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D688" t="s">
         <v>11</v>
@@ -23817,7 +23820,7 @@
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B689" t="s">
         <v>57</v>
@@ -23843,13 +23846,13 @@
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B690" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="C690" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D690" t="s">
         <v>11</v>
@@ -23869,13 +23872,13 @@
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B691" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C691" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D691" t="s">
         <v>11</v>
@@ -23895,13 +23898,13 @@
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B692" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C692" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D692" t="s">
         <v>11</v>
@@ -23921,7 +23924,7 @@
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B693" t="s">
         <v>286</v>
@@ -23947,7 +23950,7 @@
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B694" t="s">
         <v>826</v>
@@ -23973,7 +23976,7 @@
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B695" t="s">
         <v>616</v>
@@ -23999,7 +24002,7 @@
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B696" t="s">
         <v>957</v>
@@ -24025,10 +24028,10 @@
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B697" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C697" t="s">
         <v>1161</v>
@@ -24051,13 +24054,13 @@
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B698" t="s">
         <v>345</v>
       </c>
       <c r="C698" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D698" t="s">
         <v>11</v>
@@ -24077,10 +24080,10 @@
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B699" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C699" t="s">
         <v>122</v>
@@ -24103,10 +24106,10 @@
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B700" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C700" t="s">
         <v>280</v>
@@ -24129,13 +24132,13 @@
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B701" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C701" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D701" t="s">
         <v>11</v>
@@ -24155,13 +24158,13 @@
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B702" t="s">
         <v>289</v>
       </c>
       <c r="C702" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="D702" t="s">
         <v>11</v>
@@ -24181,7 +24184,7 @@
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B703" t="s">
         <v>1072</v>
@@ -24207,7 +24210,7 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B704" t="s">
         <v>1157</v>
@@ -24233,10 +24236,10 @@
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B705" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C705" t="s">
         <v>345</v>
@@ -24259,10 +24262,10 @@
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B706" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C706" t="s">
         <v>957</v>
@@ -24285,13 +24288,13 @@
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B707" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="C707" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="D707" t="s">
         <v>11</v>
@@ -24311,7 +24314,7 @@
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B708" t="s">
         <v>173</v>
@@ -24337,10 +24340,10 @@
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B709" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C709" t="s">
         <v>122</v>
@@ -24363,13 +24366,13 @@
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B710" t="s">
         <v>912</v>
       </c>
       <c r="C710" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="D710" t="s">
         <v>11</v>
@@ -24389,10 +24392,10 @@
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B711" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C711" t="s">
         <v>415</v>
@@ -24415,13 +24418,13 @@
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B712" t="s">
         <v>501</v>
       </c>
       <c r="C712" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D712" t="s">
         <v>11</v>
@@ -24441,13 +24444,13 @@
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B713" t="s">
         <v>367</v>
       </c>
       <c r="C713" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="D713" t="s">
         <v>11</v>
@@ -24467,7 +24470,7 @@
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B714" t="s">
         <v>501</v>
@@ -24493,7 +24496,7 @@
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B715" t="s">
         <v>1178</v>
@@ -24519,13 +24522,13 @@
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B716" t="s">
         <v>733</v>
       </c>
       <c r="C716" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D716" t="s">
         <v>11</v>
@@ -24545,13 +24548,13 @@
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B717" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C717" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="D717" t="s">
         <v>11</v>
@@ -24571,10 +24574,10 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B718" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C718" t="s">
         <v>733</v>
@@ -24597,7 +24600,7 @@
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B719" t="s">
         <v>91</v>
@@ -24623,7 +24626,7 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B720" t="s">
         <v>291</v>
@@ -24649,13 +24652,13 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B721" t="s">
         <v>705</v>
       </c>
       <c r="C721" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="D721" t="s">
         <v>11</v>
@@ -24675,13 +24678,13 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B722" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C722" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="D722" t="s">
         <v>11</v>
@@ -24701,13 +24704,13 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B723" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C723" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="D723" t="s">
         <v>11</v>
@@ -24727,13 +24730,13 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B724" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="C724" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="D724" t="s">
         <v>11</v>
@@ -24753,7 +24756,7 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B725" t="s">
         <v>536</v>
@@ -24779,13 +24782,13 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B726" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C726" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="D726" t="s">
         <v>11</v>
@@ -24805,13 +24808,13 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B727" t="s">
         <v>1161</v>
       </c>
       <c r="C727" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D727" t="s">
         <v>11</v>
@@ -24831,10 +24834,10 @@
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B728" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C728" t="s">
         <v>280</v>
@@ -24857,13 +24860,13 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B729" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C729" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="D729" t="s">
         <v>11</v>
@@ -24883,10 +24886,10 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B730" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C730" t="s">
         <v>122</v>
@@ -24909,7 +24912,7 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B731" t="s">
         <v>705</v>
@@ -24935,10 +24938,10 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B732" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="C732" t="s">
         <v>122</v>
@@ -24961,13 +24964,13 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B733" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C733" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="D733" t="s">
         <v>11</v>
@@ -24987,13 +24990,13 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B734" t="s">
         <v>974</v>
       </c>
       <c r="C734" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="D734" t="s">
         <v>11</v>
@@ -25013,13 +25016,13 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B735" t="s">
         <v>435</v>
       </c>
       <c r="C735" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="D735" t="s">
         <v>11</v>
@@ -25039,10 +25042,10 @@
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B736" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C736" t="s">
         <v>1053</v>
@@ -25065,7 +25068,7 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B737" t="s">
         <v>456</v>
@@ -25091,13 +25094,13 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B738" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C738" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="D738" t="s">
         <v>11</v>
@@ -25117,13 +25120,13 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B739" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C739" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D739" t="s">
         <v>11</v>
@@ -25143,13 +25146,13 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B740" t="s">
         <v>415</v>
       </c>
       <c r="C740" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="D740" t="s">
         <v>11</v>
@@ -25169,13 +25172,13 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B741" t="s">
         <v>289</v>
       </c>
       <c r="C741" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="D741" t="s">
         <v>11</v>
@@ -25195,7 +25198,7 @@
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B742" t="s">
         <v>244</v>
@@ -25221,7 +25224,7 @@
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B743" t="s">
         <v>187</v>
@@ -25247,10 +25250,10 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B744" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C744" t="s">
         <v>289</v>
@@ -25273,13 +25276,13 @@
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B745" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C745" t="s">
         <v>1515</v>
-      </c>
-      <c r="B745" t="s">
-        <v>1516</v>
-      </c>
-      <c r="C745" t="s">
-        <v>1514</v>
       </c>
       <c r="D745" t="s">
         <v>11</v>
@@ -25299,13 +25302,13 @@
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B746" t="s">
         <v>964</v>
       </c>
       <c r="C746" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D746" t="s">
         <v>11</v>
@@ -25325,10 +25328,10 @@
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B747" t="s">
         <v>1519</v>
-      </c>
-      <c r="B747" t="s">
-        <v>1518</v>
       </c>
       <c r="C747" t="s">
         <v>289</v>
@@ -25351,7 +25354,7 @@
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B748" t="s">
         <v>122</v>
@@ -25377,10 +25380,10 @@
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B749" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C749" t="s">
         <v>122</v>
@@ -25403,7 +25406,7 @@
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B750" t="s">
         <v>251</v>
@@ -25429,13 +25432,13 @@
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B751" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="C751" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D751" t="s">
         <v>11</v>
@@ -25455,7 +25458,7 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B752" t="s">
         <v>488</v>
@@ -25481,10 +25484,10 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B753" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="C753" t="s">
         <v>251</v>
@@ -25507,13 +25510,13 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B754" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C754" t="s">
         <v>1530</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1531</v>
-      </c>
-      <c r="C754" t="s">
-        <v>1529</v>
       </c>
       <c r="D754" t="s">
         <v>11</v>
@@ -25533,7 +25536,7 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B755" t="s">
         <v>91</v>
@@ -25559,7 +25562,7 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B756" t="s">
         <v>1053</v>
@@ -25585,10 +25588,10 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B757" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C757" t="s">
         <v>392</v>
@@ -25611,10 +25614,10 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B758" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C758" t="s">
         <v>251</v>
@@ -25637,7 +25640,7 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B759" t="s">
         <v>561</v>
@@ -25663,10 +25666,10 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B760" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="C760" t="s">
         <v>1053</v>
@@ -25689,13 +25692,13 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B761" t="s">
         <v>582</v>
       </c>
       <c r="C761" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D761" t="s">
         <v>11</v>
@@ -25715,7 +25718,7 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B762" t="s">
         <v>1079</v>
@@ -25741,7 +25744,7 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B763" t="s">
         <v>1125</v>
@@ -25767,13 +25770,13 @@
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B764" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="C764" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="D764" t="s">
         <v>11</v>
@@ -25793,7 +25796,7 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B765" t="s">
         <v>1125</v>
@@ -25819,10 +25822,10 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B766" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="C766" t="s">
         <v>343</v>
@@ -25845,10 +25848,10 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B767" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C767" t="s">
         <v>1125</v>
@@ -25871,7 +25874,7 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B768" t="s">
         <v>30</v>
@@ -25897,10 +25900,10 @@
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B769" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C769" t="s">
         <v>427</v>
@@ -25923,10 +25926,10 @@
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B770" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="C770" t="s">
         <v>1126</v>
@@ -25949,10 +25952,10 @@
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B771" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C771" t="s">
         <v>543</v>
@@ -25975,13 +25978,13 @@
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B772" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C772" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="D772" t="s">
         <v>11</v>
@@ -26001,13 +26004,13 @@
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B773" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="C773" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="D773" t="s">
         <v>11</v>
@@ -26027,13 +26030,13 @@
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B774" t="s">
         <v>1018</v>
       </c>
       <c r="C774" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D774" t="s">
         <v>11</v>
@@ -26053,10 +26056,10 @@
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B775" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="C775" t="s">
         <v>476</v>
@@ -26079,13 +26082,13 @@
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B776" t="s">
         <v>91</v>
       </c>
       <c r="C776" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D776" t="s">
         <v>11</v>
@@ -26105,13 +26108,13 @@
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B777" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C777" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D777" t="s">
         <v>11</v>
@@ -26131,7 +26134,7 @@
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B778" t="s">
         <v>964</v>
@@ -26157,7 +26160,7 @@
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B779" t="s">
         <v>105</v>
@@ -26183,13 +26186,13 @@
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B780" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="C780" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="D780" t="s">
         <v>11</v>
@@ -26209,10 +26212,10 @@
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B781" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C781" t="s">
         <v>96</v>
@@ -26235,13 +26238,13 @@
     </row>
     <row r="782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B782" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="C782" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="D782" t="s">
         <v>11</v>
@@ -26261,7 +26264,7 @@
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B783" t="s">
         <v>187</v>
@@ -26287,7 +26290,7 @@
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B784" t="s">
         <v>399</v>
@@ -26313,10 +26316,10 @@
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B785" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="C785" t="s">
         <v>1183</v>
@@ -26339,7 +26342,7 @@
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B786" t="s">
         <v>579</v>
@@ -26365,13 +26368,13 @@
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B787" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C787" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D787" t="s">
         <v>11</v>
@@ -26391,10 +26394,10 @@
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B788" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C788" t="s">
         <v>91</v>
@@ -26417,13 +26420,13 @@
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B789" t="s">
         <v>733</v>
       </c>
       <c r="C789" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D789" t="s">
         <v>11</v>
@@ -26443,10 +26446,10 @@
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B790" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C790" t="s">
         <v>733</v>
@@ -26469,13 +26472,13 @@
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B791" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C791" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="D791" t="s">
         <v>11</v>
@@ -26495,13 +26498,13 @@
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B792" t="s">
         <v>204</v>
       </c>
       <c r="C792" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D792" t="s">
         <v>11</v>
@@ -26521,13 +26524,13 @@
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B793" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="C793" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="D793" t="s">
         <v>11</v>
@@ -26547,7 +26550,7 @@
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B794" t="s">
         <v>208</v>
@@ -26573,7 +26576,7 @@
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B795" t="s">
         <v>506</v>
@@ -26599,13 +26602,13 @@
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B796" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="C796" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D796" t="s">
         <v>11</v>
@@ -26625,13 +26628,13 @@
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B797" t="s">
         <v>204</v>
       </c>
       <c r="C797" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D797" t="s">
         <v>11</v>
@@ -26651,13 +26654,13 @@
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B798" t="s">
         <v>892</v>
       </c>
       <c r="C798" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="D798" t="s">
         <v>11</v>
@@ -26677,13 +26680,13 @@
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B799" t="s">
         <v>998</v>
       </c>
       <c r="C799" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D799" t="s">
         <v>11</v>
@@ -26703,13 +26706,13 @@
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B800" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="C800" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="D800" t="s">
         <v>11</v>
@@ -26729,13 +26732,13 @@
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B801" t="s">
         <v>561</v>
       </c>
       <c r="C801" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D801" t="s">
         <v>11</v>
@@ -26755,10 +26758,10 @@
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B802" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="C802" t="s">
         <v>807</v>
@@ -26781,13 +26784,13 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B803" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="C803" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D803" t="s">
         <v>11</v>
@@ -26807,13 +26810,13 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B804" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="C804" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="D804" t="s">
         <v>11</v>
@@ -26833,13 +26836,13 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B805" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="C805" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D805" t="s">
         <v>11</v>
@@ -26859,13 +26862,13 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B806" t="s">
         <v>598</v>
       </c>
       <c r="C806" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="D806" t="s">
         <v>11</v>
@@ -26885,13 +26888,13 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B807" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C807" t="s">
         <v>1614</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C807" t="s">
-        <v>1613</v>
       </c>
       <c r="D807" t="s">
         <v>11</v>
@@ -26911,13 +26914,13 @@
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B808" t="s">
         <v>328</v>
       </c>
       <c r="C808" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D808" t="s">
         <v>11</v>
@@ -26937,13 +26940,13 @@
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B809" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="C809" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="D809" t="s">
         <v>11</v>
@@ -26963,13 +26966,13 @@
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B810" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="C810" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="D810" t="s">
         <v>11</v>
@@ -26989,10 +26992,10 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B811" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="C811" t="s">
         <v>598</v>
@@ -27015,13 +27018,13 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B812" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="C812" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="D812" t="s">
         <v>11</v>
@@ -27041,10 +27044,10 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B813" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="C813" t="s">
         <v>328</v>
@@ -27067,13 +27070,13 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B814" t="s">
         <v>415</v>
       </c>
       <c r="C814" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="D814" t="s">
         <v>11</v>
@@ -27093,7 +27096,7 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B815" t="s">
         <v>1125</v>
@@ -27119,10 +27122,10 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B816" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="C816" t="s">
         <v>824</v>
@@ -27145,10 +27148,10 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B817" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="C817" t="s">
         <v>51</v>
@@ -27171,10 +27174,10 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B818" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C818" t="s">
         <v>328</v>
@@ -27197,13 +27200,13 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B819" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="C819" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="D819" t="s">
         <v>11</v>
@@ -27223,13 +27226,13 @@
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B820" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="C820" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D820" t="s">
         <v>11</v>
@@ -27249,13 +27252,13 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B821" t="s">
         <v>446</v>
       </c>
       <c r="C821" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="D821" t="s">
         <v>11</v>
@@ -27275,7 +27278,7 @@
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B822" t="s">
         <v>826</v>
@@ -27301,10 +27304,10 @@
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B823" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="C823" t="s">
         <v>546</v>
@@ -27327,13 +27330,13 @@
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B824" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="C824" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D824" t="s">
         <v>11</v>
@@ -27353,13 +27356,13 @@
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B825" t="s">
         <v>871</v>
       </c>
       <c r="C825" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D825" t="s">
         <v>11</v>
@@ -27379,10 +27382,10 @@
     </row>
     <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B826" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="C826" t="s">
         <v>871</v>
@@ -27405,13 +27408,13 @@
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B827" t="s">
         <v>909</v>
       </c>
       <c r="C827" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D827" t="s">
         <v>11</v>
@@ -27431,13 +27434,13 @@
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B828" t="s">
         <v>355</v>
       </c>
       <c r="C828" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D828" t="s">
         <v>11</v>
@@ -27457,7 +27460,7 @@
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B829" t="s">
         <v>104</v>
@@ -27483,10 +27486,10 @@
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B830" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C830" t="s">
         <v>909</v>
@@ -27509,13 +27512,13 @@
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B831" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="C831" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D831" t="s">
         <v>11</v>
@@ -27535,7 +27538,7 @@
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B832" t="s">
         <v>565</v>
@@ -27561,10 +27564,10 @@
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B833" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="C833" t="s">
         <v>329</v>
@@ -27587,7 +27590,7 @@
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B834" t="s">
         <v>101</v>
@@ -27613,13 +27616,13 @@
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B835" t="s">
         <v>71</v>
       </c>
       <c r="C835" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="D835" t="s">
         <v>11</v>
@@ -27639,10 +27642,10 @@
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B836" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C836" t="s">
         <v>71</v>
@@ -27665,13 +27668,13 @@
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B837" t="s">
         <v>1178</v>
       </c>
       <c r="C837" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D837" t="s">
         <v>11</v>
@@ -27691,10 +27694,10 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B838" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="C838" t="s">
         <v>585</v>
@@ -27717,13 +27720,13 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B839" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="C839" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="D839" t="s">
         <v>11</v>
@@ -27743,13 +27746,13 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B840" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C840" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="D840" t="s">
         <v>11</v>
@@ -27769,13 +27772,13 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B841" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C841" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="D841" t="s">
         <v>11</v>
@@ -27795,13 +27798,13 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B842" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C842" t="s">
         <v>1678</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C842" t="s">
-        <v>1677</v>
       </c>
       <c r="D842" t="s">
         <v>11</v>
@@ -27821,10 +27824,10 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B843" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="C843" t="s">
         <v>1090</v>
@@ -27847,7 +27850,7 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B844" t="s">
         <v>1009</v>
@@ -27873,7 +27876,7 @@
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B845" t="s">
         <v>904</v>
@@ -27899,13 +27902,13 @@
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B846" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="C846" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="D846" t="s">
         <v>11</v>
@@ -27925,10 +27928,10 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B847" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="C847" t="s">
         <v>1053</v>
@@ -27951,13 +27954,13 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B848" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="C848" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="D848" t="s">
         <v>11</v>
@@ -27977,13 +27980,13 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B849" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C849" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D849" t="s">
         <v>11</v>
@@ -28003,13 +28006,13 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B850" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="C850" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D850" t="s">
         <v>11</v>
@@ -28029,10 +28032,10 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B851" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="C851" t="s">
         <v>488</v>
@@ -28055,7 +28058,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B852" t="s">
         <v>700</v>
@@ -28081,7 +28084,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B853" t="s">
         <v>624</v>
@@ -28107,7 +28110,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B854" t="s">
         <v>33</v>
@@ -28133,10 +28136,10 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B855" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="C855" t="s">
         <v>706</v>
@@ -28159,13 +28162,13 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B856" t="s">
         <v>974</v>
       </c>
       <c r="C856" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="D856" t="s">
         <v>11</v>
@@ -28185,13 +28188,13 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C857" t="s">
         <v>1703</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1704</v>
-      </c>
-      <c r="C857" t="s">
-        <v>1702</v>
       </c>
       <c r="D857" t="s">
         <v>11</v>
@@ -28211,10 +28214,10 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B858" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="C858" t="s">
         <v>122</v>
@@ -28237,13 +28240,13 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B859" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="C859" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D859" t="s">
         <v>11</v>
@@ -28263,13 +28266,13 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B860" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C860" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="D860" t="s">
         <v>11</v>
@@ -28289,13 +28292,13 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B861" t="s">
         <v>23</v>
       </c>
       <c r="C861" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="D861" t="s">
         <v>11</v>
@@ -28315,13 +28318,13 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B862" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="C862" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="D862" t="s">
         <v>11</v>
@@ -28341,10 +28344,10 @@
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B863" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="C863" t="s">
         <v>536</v>
@@ -28367,10 +28370,10 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B864" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="C864" t="s">
         <v>695</v>
@@ -28393,7 +28396,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B865" t="s">
         <v>401</v>
@@ -28419,7 +28422,7 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B866" t="s">
         <v>512</v>
@@ -28445,7 +28448,7 @@
     </row>
     <row r="867" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B867" t="s">
         <v>478</v>
@@ -28471,10 +28474,10 @@
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B868" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="C868" t="s">
         <v>498</v>
@@ -28497,13 +28500,13 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B869" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="C869" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="D869" t="s">
         <v>11</v>
@@ -28523,10 +28526,10 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B870" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C870" t="s">
         <v>201</v>
@@ -28549,7 +28552,7 @@
     </row>
     <row r="871" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B871" t="s">
         <v>977</v>
@@ -28575,13 +28578,13 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B872" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C872" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D872" t="s">
         <v>11</v>
@@ -28601,10 +28604,10 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B873" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C873" t="s">
         <v>971</v>
@@ -28627,10 +28630,10 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B874" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="C874" t="s">
         <v>30</v>
@@ -28653,13 +28656,13 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B875" t="s">
         <v>51</v>
       </c>
       <c r="C875" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="D875" t="s">
         <v>11</v>
@@ -28679,10 +28682,10 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B876" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="C876" t="s">
         <v>1125</v>
@@ -28705,13 +28708,13 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B877" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C877" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="D877" t="s">
         <v>11</v>
@@ -28731,13 +28734,13 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B878" t="s">
         <v>394</v>
       </c>
       <c r="C878" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D878" t="s">
         <v>11</v>
@@ -28757,13 +28760,13 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B879" t="s">
         <v>733</v>
       </c>
       <c r="C879" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D879" t="s">
         <v>11</v>
@@ -28783,7 +28786,7 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B880" t="s">
         <v>27</v>
@@ -28809,7 +28812,7 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B881" t="s">
         <v>28</v>
@@ -28835,7 +28838,7 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B882" t="s">
         <v>425</v>
@@ -28861,7 +28864,7 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B883" t="s">
         <v>208</v>
@@ -28887,7 +28890,7 @@
     </row>
     <row r="884" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B884" t="s">
         <v>423</v>
@@ -28913,10 +28916,10 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B885" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="C885" t="s">
         <v>1043</v>
@@ -28939,7 +28942,7 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B886" t="s">
         <v>421</v>
@@ -28965,13 +28968,13 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B887" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C887" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="D887" t="s">
         <v>11</v>
@@ -28991,13 +28994,13 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B888" t="s">
         <v>540</v>
       </c>
       <c r="C888" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="D888" t="s">
         <v>11</v>
@@ -29017,13 +29020,13 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B889" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="C889" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="D889" t="s">
         <v>11</v>
@@ -29043,10 +29046,10 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B890" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="C890" t="s">
         <v>102</v>
@@ -29069,13 +29072,13 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B891" t="s">
         <v>1167</v>
       </c>
       <c r="C891" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="D891" t="s">
         <v>11</v>
@@ -29095,13 +29098,13 @@
     </row>
     <row r="892" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B892" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="C892" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="D892" t="s">
         <v>11</v>
@@ -29121,10 +29124,10 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B893" t="s">
         <v>1764</v>
-      </c>
-      <c r="B893" t="s">
-        <v>1763</v>
       </c>
       <c r="C893" t="s">
         <v>598</v>
@@ -29147,10 +29150,10 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B894" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C894" t="s">
         <v>598</v>
@@ -29173,13 +29176,13 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B895" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="C895" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="D895" t="s">
         <v>11</v>
@@ -29199,13 +29202,13 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B896" t="s">
         <v>236</v>
       </c>
       <c r="C896" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="D896" t="s">
         <v>11</v>
@@ -29225,13 +29228,13 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B897" t="s">
         <v>322</v>
       </c>
       <c r="C897" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="D897" t="s">
         <v>11</v>
@@ -29251,10 +29254,10 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B898" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C898" t="s">
         <v>685</v>
@@ -29277,7 +29280,7 @@
     </row>
     <row r="899" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B899" t="s">
         <v>733</v>
@@ -29303,10 +29306,10 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B900" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C900" t="s">
         <v>685</v>
@@ -29329,7 +29332,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B901" t="s">
         <v>1125</v>
@@ -29355,13 +29358,13 @@
     </row>
     <row r="902" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B902" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="C902" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="D902" t="s">
         <v>11</v>
@@ -29381,13 +29384,13 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B903" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="C903" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="D903" t="s">
         <v>11</v>
@@ -29407,13 +29410,13 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B904" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="C904" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="D904" t="s">
         <v>11</v>
@@ -29433,13 +29436,13 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B905" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="C905" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D905" t="s">
         <v>11</v>
@@ -29459,10 +29462,10 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B906" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C906" t="s">
         <v>541</v>
@@ -29485,13 +29488,13 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B907" t="s">
         <v>213</v>
       </c>
       <c r="C907" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="D907" t="s">
         <v>11</v>
@@ -29511,10 +29514,10 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B908" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C908" t="s">
         <v>733</v>
@@ -29537,10 +29540,10 @@
     </row>
     <row r="909" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B909" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="C909" t="s">
         <v>307</v>
@@ -29563,10 +29566,10 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B910" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="C910" t="s">
         <v>548</v>
@@ -29589,13 +29592,13 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B911" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="C911" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D911" t="s">
         <v>11</v>
@@ -29615,10 +29618,10 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B912" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C912" t="s">
         <v>583</v>
@@ -29641,13 +29644,13 @@
     </row>
     <row r="913" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B913" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="C913" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D913" t="s">
         <v>11</v>
@@ -29667,10 +29670,10 @@
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B914" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C914" t="s">
         <v>541</v>
@@ -29693,7 +29696,7 @@
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B915" t="s">
         <v>124</v>
@@ -29719,13 +29722,13 @@
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B916" t="s">
         <v>750</v>
       </c>
       <c r="C916" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="D916" t="s">
         <v>11</v>
@@ -29745,13 +29748,13 @@
     </row>
     <row r="917" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B917" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C917" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="D917" t="s">
         <v>11</v>
@@ -29771,7 +29774,7 @@
     </row>
     <row r="918" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B918" t="s">
         <v>859</v>
@@ -29797,13 +29800,13 @@
     </row>
     <row r="919" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B919" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="C919" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D919" t="s">
         <v>11</v>
@@ -29823,7 +29826,7 @@
     </row>
     <row r="920" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B920" t="s">
         <v>286</v>
@@ -29849,13 +29852,13 @@
     </row>
     <row r="921" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B921" t="s">
         <v>51</v>
       </c>
       <c r="C921" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="D921" t="s">
         <v>11</v>
@@ -29875,13 +29878,13 @@
     </row>
     <row r="922" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B922" t="s">
         <v>291</v>
       </c>
       <c r="C922" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="D922" t="s">
         <v>11</v>
@@ -29901,13 +29904,13 @@
     </row>
     <row r="923" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B923" t="s">
         <v>773</v>
       </c>
       <c r="C923" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="D923" t="s">
         <v>11</v>
@@ -29927,13 +29930,13 @@
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B924" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="C924" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="D924" t="s">
         <v>11</v>
@@ -29953,10 +29956,10 @@
     </row>
     <row r="925" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B925" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="C925" t="s">
         <v>33</v>
@@ -29979,13 +29982,13 @@
     </row>
     <row r="926" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B926" t="s">
         <v>1172</v>
       </c>
       <c r="C926" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="D926" t="s">
         <v>11</v>
@@ -30005,13 +30008,13 @@
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B927" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C927" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="D927" t="s">
         <v>11</v>
@@ -30031,13 +30034,13 @@
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B928" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C928" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="D928" t="s">
         <v>11</v>
@@ -30057,10 +30060,10 @@
     </row>
     <row r="929" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B929" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="C929" t="s">
         <v>122</v>
@@ -30083,10 +30086,10 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B930" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="C930" t="s">
         <v>1125</v>
@@ -30109,13 +30112,13 @@
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B931" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C931" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="D931" t="s">
         <v>11</v>
@@ -30135,7 +30138,7 @@
     </row>
     <row r="932" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B932" t="s">
         <v>312</v>
@@ -30161,10 +30164,10 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B933" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="C933" t="s">
         <v>497</v>
@@ -30187,10 +30190,10 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B934" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="C934" t="s">
         <v>497</v>
@@ -30213,10 +30216,10 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B935" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C935" t="s">
         <v>561</v>
@@ -30239,7 +30242,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B936" t="s">
         <v>475</v>
@@ -30265,7 +30268,7 @@
     </row>
     <row r="937" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B937" t="s">
         <v>145</v>
@@ -30291,7 +30294,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B938" t="s">
         <v>33</v>
@@ -30317,10 +30320,10 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B939" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C939" t="s">
         <v>475</v>
@@ -30343,7 +30346,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B940" t="s">
         <v>272</v>
